--- a/branches/dev/v2027/StructureDefinition-mii-lm-patho-logical-model.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-lm-patho-logical-model.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:30:15+00:00</t>
+    <t>2026-09-14T08:48:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-lm-patho-logical-model.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-lm-patho-logical-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:48:26+00:00</t>
+    <t>2026-09-14T10:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/v2027/StructureDefinition-mii-lm-patho-logical-model.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-lm-patho-logical-model.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T10:17:23+00:00</t>
+    <t>2026-09-14T10:33:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
